--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estadisticas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Estadisticas" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,58 +413,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tema</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>pregunta_corta</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pregunta_completa</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>intentos</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>aciertos</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>fallos</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>pct_fallos</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>pct_aciertos</t>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>porcentaje_fallos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>porcentaje_aciertos</t>
         </is>
       </c>
     </row>
@@ -2589,6 +2567,38 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>B Completo revistas</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>20. La mejor forma de recuperarse de la fatiga cua</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>20. La mejor forma de recuperarse de la fatiga cuando se conduce, es...</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2602,6 +2602,38 @@
         <v>100</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>B Completo revistas</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>13. ¿Cuál es la velocidad máxima genérica para un</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>13. ¿Cuál es la velocidad máxima genérica para un turismo en autovía?</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2634,6 +2634,38 @@
         <v>100</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>B Completo revistas</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2. Para que pueda circular un ciclomotor, ¿es obli</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2. Para que pueda circular un ciclomotor, ¿es obligatorio que esté asegurado?</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -2642,12 +2642,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2. Para que pueda circular un ciclomotor, ¿es obli</t>
+          <t>27. Cuando llueve o hay viento, ¿por qué hay que t</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2. Para que pueda circular un ciclomotor, ¿es obligatorio que esté asegurado?</t>
+          <t>27. Cuando llueve o hay viento, ¿por qué hay que tener más precaución con los ciclistas?</t>
         </is>
       </c>
       <c r="D70" t="n">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2666,6 +2666,38 @@
         <v>100</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>B Completo revistas</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>25. En caso de contradicción entre señales del mis</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>25. En caso de contradicción entre señales del mismo tipo, ¿cuál prevalecerá?</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -2695,6 +2695,38 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>B Completo revistas</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>30. Esta señal indica peligro por la proximidad de</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>30. Esta señal indica peligro por la proximidad de...</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2730,6 +2730,38 @@
         <v>100</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>B Completo revistas</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1. Circulando con lluvia muy intensa, ¿es correcto</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1. Circulando con lluvia muy intensa, ¿es correcto encender la luz antiniebla trasera?</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -2695,70 +2695,6 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>B Completo revistas</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>30. Esta señal indica peligro por la proximidad de</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>30. Esta señal indica peligro por la proximidad de...</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" t="n">
-        <v>1</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>B Completo revistas</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>1. Circulando con lluvia muy intensa, ¿es correcto</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>1. Circulando con lluvia muy intensa, ¿es correcto encender la luz antiniebla trasera?</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -2695,6 +2695,102 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>B Completo revistas</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>30. Esta señal indica peligro por la proximidad de</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>30. Esta señal indica peligro por la proximidad de...</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>B Completo revistas</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1. Circulando con lluvia muy intensa, ¿es correcto</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1. Circulando con lluvia muy intensa, ¿es correcto encender la luz antiniebla trasera?</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>B Completo revistas</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>7. La distancia de detención puede variar en funci</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>7. La distancia de detención puede variar en función...</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -2706,12 +2706,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30. Esta señal indica peligro por la proximidad de</t>
+          <t>3. Los conductores jóvenes suelen tener más accide</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>30. Esta señal indica peligro por la proximidad de...</t>
+          <t>3. Los conductores jóvenes suelen tener más accidentes...</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2727,70 +2727,6 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>B Completo revistas</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>1. Circulando con lluvia muy intensa, ¿es correcto</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>1. Circulando con lluvia muy intensa, ¿es correcto encender la luz antiniebla trasera?</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>B Completo revistas</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>7. La distancia de detención puede variar en funci</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>7. La distancia de detención puede variar en función...</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>1</v>
-      </c>
-      <c r="E74" t="n">
-        <v>1</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -2706,12 +2706,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>3. Los conductores jóvenes suelen tener más accide</t>
+          <t>30. Esta señal indica peligro por la proximidad de</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>3. Los conductores jóvenes suelen tener más accidentes...</t>
+          <t>30. Esta señal indica peligro por la proximidad de...</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2727,6 +2727,102 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>B Completo revistas</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1. Circulando con lluvia muy intensa, ¿es correcto</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1. Circulando con lluvia muy intensa, ¿es correcto encender la luz antiniebla trasera?</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>B Completo revistas</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>7. La distancia de detención puede variar en funci</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>7. La distancia de detención puede variar en función...</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>B Completo revistas</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>24. En una vía urbana de sentido único, si los car</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>24. En una vía urbana de sentido único, si los carriles no están delimitados por marcas viales, ¿por dónde está obligado a circular el conductor de un turismo?</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -2706,12 +2706,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30. Esta señal indica peligro por la proximidad de</t>
+          <t>3. Los conductores jóvenes suelen tener más accide</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>30. Esta señal indica peligro por la proximidad de...</t>
+          <t>3. Los conductores jóvenes suelen tener más accidentes...</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1. Circulando con lluvia muy intensa, ¿es correcto</t>
+          <t>15. El conductor está obligado a advertir mediante</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1. Circulando con lluvia muy intensa, ¿es correcto encender la luz antiniebla trasera?</t>
+          <t>15. El conductor está obligado a advertir mediante señales ópticas...</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2759,70 +2759,6 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>B Completo revistas</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>7. La distancia de detención puede variar en funci</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>7. La distancia de detención puede variar en función...</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>1</v>
-      </c>
-      <c r="E74" t="n">
-        <v>1</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>B Completo revistas</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>24. En una vía urbana de sentido único, si los car</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>24. En una vía urbana de sentido único, si los carriles no están delimitados por marcas viales, ¿por dónde está obligado a circular el conductor de un turismo?</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>1</v>
-      </c>
-      <c r="E75" t="n">
-        <v>1</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2762,6 +2762,38 @@
         <v>100</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>B Completo revistas</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>16. Para seguir de frente, ¿dónde hay que deteners</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>16. Para seguir de frente, ¿dónde hay que detenerse?</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2794,6 +2794,38 @@
         <v>100</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>B Completo revistas</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>19. ¿Puede circular con su motocicleta por un carr</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>19. ¿Puede circular con su motocicleta por un carril bus?</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -2791,38 +2791,6 @@
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>B Completo revistas</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>19. ¿Puede circular con su motocicleta por un carr</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>19. ¿Puede circular con su motocicleta por un carril bus?</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>1</v>
-      </c>
-      <c r="E75" t="n">
-        <v>1</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2794,6 +2794,38 @@
         <v>100</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>B Completo revistas</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>23. ¿Qué indica la señal?</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>23. ¿Qué indica la señal?</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -2802,12 +2802,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>23. ¿Qué indica la señal?</t>
+          <t>6. Al adelantar al ciclista que aparece en la foto</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>23. ¿Qué indica la señal?</t>
+          <t>6. Al adelantar al ciclista que aparece en la fotografía, ¿es obligatorio invadir el carril de sentido contrario de la calzada?</t>
         </is>
       </c>
       <c r="D75" t="n">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2826,6 +2826,38 @@
         <v>100</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>B Completo revistas</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>19. ¿Puede circular con su motocicleta por un carr</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>19. ¿Puede circular con su motocicleta por un carril bus?</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2858,6 +2858,38 @@
         <v>100</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>B Completo revistas</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>23. ¿Qué indica la señal?</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>23. ¿Qué indica la señal?</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,33 +589,33 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T4 aje</t>
+          <t>DGT Junio 26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>En caso de avería del alumbrado de corto alcance,</t>
+          <t>¿Qué significa está señal?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>En caso de avería del alumbrado de corto alcance, ¿puede circular fuera de poblado por una vía insuficientemente iluminada con el alumbrado de largo alcance?</t>
+          <t>¿Qué significa está señal?</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H6" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -626,12 +626,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Si no puede alcanzar con su vehículo la velocidad</t>
+          <t>En caso de avería del alumbrado de corto alcance,</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Si no puede alcanzar con su vehículo la velocidad mínima exigida en la vía por la que circula y existe peligro de alcance, ¿qué debe hacer?</t>
+          <t>En caso de avería del alumbrado de corto alcance, ¿puede circular fuera de poblado por una vía insuficientemente iluminada con el alumbrado de largo alcance?</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -658,12 +658,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>La luz antiniebla trasera deberá utilizarse en cas</t>
+          <t>Si no puede alcanzar con su vehículo la velocidad</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>La luz antiniebla trasera deberá utilizarse en caso de...</t>
+          <t>Si no puede alcanzar con su vehículo la velocidad mínima exigida en la vía por la que circula y existe peligro de alcance, ¿qué debe hacer?</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -690,12 +690,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Para no deslumbrar a otros usuarios deberá...</t>
+          <t>La luz antiniebla trasera deberá utilizarse en cas</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Para no deslumbrar a otros usuarios deberá...</t>
+          <t>La luz antiniebla trasera deberá utilizarse en caso de...</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -722,12 +722,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Durante el día, el conductor de un turismo, ¿cuánd</t>
+          <t>Para no deslumbrar a otros usuarios deberá...</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Durante el día, el conductor de un turismo, ¿cuándo está obligado a circular con el alumbrado de corto alcance encendido?</t>
+          <t>Para no deslumbrar a otros usuarios deberá...</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -754,12 +754,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>En condiciones que disminuyen sensiblemente la vis</t>
+          <t>Durante el día, el conductor de un turismo, ¿cuánd</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>En condiciones que disminuyen sensiblemente la visibilidad, como en caso de niebla, ¿está permitido encender solo el alumbrado de posición y el de cruce?</t>
+          <t>Durante el día, el conductor de un turismo, ¿cuándo está obligado a circular con el alumbrado de corto alcance encendido?</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -781,17 +781,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DGT Junio 26</t>
+          <t>T4 aje</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Un turismo, ¿cuándo puede superar la velocidad máx</t>
+          <t>En condiciones que disminuyen sensiblemente la vis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Un turismo, ¿cuándo puede superar la velocidad máxima genérica en 20 km/h?</t>
+          <t>En condiciones que disminuyen sensiblemente la visibilidad, como en caso de niebla, ¿está permitido encender solo el alumbrado de posición y el de cruce?</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -818,12 +818,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Para evitar o retrasar la fatiga, los conductores</t>
+          <t>Un turismo, ¿cuándo puede superar la velocidad máx</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Para evitar o retrasar la fatiga, los conductores deben...</t>
+          <t>Un turismo, ¿cuándo puede superar la velocidad máxima genérica en 20 km/h?</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -850,12 +850,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>La mayoría de los accidentes se deben...</t>
+          <t>Para evitar o retrasar la fatiga, los conductores</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>La mayoría de los accidentes se deben...</t>
+          <t>Para evitar o retrasar la fatiga, los conductores deben...</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -882,12 +882,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Por el carril de alta ocupación VAO, ¿puede circul</t>
+          <t>La mayoría de los accidentes se deben...</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Por el carril de alta ocupación VAO, ¿puede circular un turismo con remolque?</t>
+          <t>La mayoría de los accidentes se deben...</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -914,12 +914,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>En una carretera convencional, ¿está permitido que</t>
+          <t>Por el carril de alta ocupación VAO, ¿puede circul</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>En una carretera convencional, ¿está permitido que un peatón circule por la calzada?</t>
+          <t>Por el carril de alta ocupación VAO, ¿puede circular un turismo con remolque?</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -946,12 +946,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>¿Qué significa está señal?</t>
+          <t>En una carretera convencional, ¿está permitido que</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>¿Qué significa está señal?</t>
+          <t>En una carretera convencional, ¿está permitido que un peatón circule por la calzada?</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -2887,6 +2887,38 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>B Completo revistas</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>4. La vía, su entorno y el propio vehículo, ¿puede</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>4. La vía, su entorno y el propio vehículo, ¿pueden favorecer la aparición de distracciones al volante?</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,17 +493,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DGT Junio 26</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>¿Cuál es la velocidad máxima en una vía urbana con</t>
+          <t>Para obedecer esta señal de stop, ¿dónde debe dete</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>¿Cuál es la velocidad máxima en una vía urbana con un único carril por sentido de circulación?</t>
+          <t>Para obedecer esta señal de stop, ¿dónde debe detenerse si existe suficiente visibilidad?</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -525,17 +525,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Para obedecer esta señal de stop, ¿dónde debe dete</t>
+          <t>Relativo a la disposición de la carga en un vehícu</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Para obedecer esta señal de stop, ¿dónde debe detenerse si existe suficiente visibilidad?</t>
+          <t>Relativo a la disposición de la carga en un vehículo, ¿cómo es obligatorio transportar siempre las materias que produzcan polvo o puedan caer?</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -557,65 +557,65 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T05</t>
+          <t>DGT Junio 26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Relativo a la disposición de la carga en un vehícu</t>
+          <t>¿Cuál es la velocidad máxima en una vía urbana con</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Relativo a la disposición de la carga en un vehículo, ¿cómo es obligatorio transportar siempre las materias que produzcan polvo o puedan caer?</t>
+          <t>¿Cuál es la velocidad máxima en una vía urbana con un único carril por sentido de circulación?</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DGT Junio 26</t>
+          <t>T4 aje</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>¿Qué significa está señal?</t>
+          <t>En caso de avería del alumbrado de corto alcance,</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>¿Qué significa está señal?</t>
+          <t>En caso de avería del alumbrado de corto alcance, ¿puede circular fuera de poblado por una vía insuficientemente iluminada con el alumbrado de largo alcance?</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -626,12 +626,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>En caso de avería del alumbrado de corto alcance,</t>
+          <t>Si no puede alcanzar con su vehículo la velocidad</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>En caso de avería del alumbrado de corto alcance, ¿puede circular fuera de poblado por una vía insuficientemente iluminada con el alumbrado de largo alcance?</t>
+          <t>Si no puede alcanzar con su vehículo la velocidad mínima exigida en la vía por la que circula y existe peligro de alcance, ¿qué debe hacer?</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -658,12 +658,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Si no puede alcanzar con su vehículo la velocidad</t>
+          <t>La luz antiniebla trasera deberá utilizarse en cas</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Si no puede alcanzar con su vehículo la velocidad mínima exigida en la vía por la que circula y existe peligro de alcance, ¿qué debe hacer?</t>
+          <t>La luz antiniebla trasera deberá utilizarse en caso de...</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -690,12 +690,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>La luz antiniebla trasera deberá utilizarse en cas</t>
+          <t>Para no deslumbrar a otros usuarios deberá...</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>La luz antiniebla trasera deberá utilizarse en caso de...</t>
+          <t>Para no deslumbrar a otros usuarios deberá...</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -722,12 +722,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Para no deslumbrar a otros usuarios deberá...</t>
+          <t>Durante el día, el conductor de un turismo, ¿cuánd</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Para no deslumbrar a otros usuarios deberá...</t>
+          <t>Durante el día, el conductor de un turismo, ¿cuándo está obligado a circular con el alumbrado de corto alcance encendido?</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -754,12 +754,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Durante el día, el conductor de un turismo, ¿cuánd</t>
+          <t>En condiciones que disminuyen sensiblemente la vis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Durante el día, el conductor de un turismo, ¿cuándo está obligado a circular con el alumbrado de corto alcance encendido?</t>
+          <t>En condiciones que disminuyen sensiblemente la visibilidad, como en caso de niebla, ¿está permitido encender solo el alumbrado de posición y el de cruce?</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -781,17 +781,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T4 aje</t>
+          <t>DGT Junio 26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>En condiciones que disminuyen sensiblemente la vis</t>
+          <t>Un turismo, ¿cuándo puede superar la velocidad máx</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>En condiciones que disminuyen sensiblemente la visibilidad, como en caso de niebla, ¿está permitido encender solo el alumbrado de posición y el de cruce?</t>
+          <t>Un turismo, ¿cuándo puede superar la velocidad máxima genérica en 20 km/h?</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -818,12 +818,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Un turismo, ¿cuándo puede superar la velocidad máx</t>
+          <t>Para evitar o retrasar la fatiga, los conductores</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Un turismo, ¿cuándo puede superar la velocidad máxima genérica en 20 km/h?</t>
+          <t>Para evitar o retrasar la fatiga, los conductores deben...</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -850,12 +850,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Para evitar o retrasar la fatiga, los conductores</t>
+          <t>La mayoría de los accidentes se deben...</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Para evitar o retrasar la fatiga, los conductores deben...</t>
+          <t>La mayoría de los accidentes se deben...</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -882,12 +882,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>La mayoría de los accidentes se deben...</t>
+          <t>Por el carril de alta ocupación VAO, ¿puede circul</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>La mayoría de los accidentes se deben...</t>
+          <t>Por el carril de alta ocupación VAO, ¿puede circular un turismo con remolque?</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -914,12 +914,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Por el carril de alta ocupación VAO, ¿puede circul</t>
+          <t>En una carretera convencional, ¿está permitido que</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Por el carril de alta ocupación VAO, ¿puede circular un turismo con remolque?</t>
+          <t>En una carretera convencional, ¿está permitido que un peatón circule por la calzada?</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -946,12 +946,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>En una carretera convencional, ¿está permitido que</t>
+          <t>¿Qué significa está señal?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>En una carretera convencional, ¿está permitido que un peatón circule por la calzada?</t>
+          <t>¿Qué significa está señal?</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -2887,38 +2887,6 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>B Completo revistas</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>4. La vía, su entorno y el propio vehículo, ¿puede</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>4. La vía, su entorno y el propio vehículo, ¿pueden favorecer la aparición de distracciones al volante?</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,17 +493,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>DGT Junio 26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Para obedecer esta señal de stop, ¿dónde debe dete</t>
+          <t>¿Cuál es la velocidad máxima en una vía urbana con</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Para obedecer esta señal de stop, ¿dónde debe detenerse si existe suficiente visibilidad?</t>
+          <t>¿Cuál es la velocidad máxima en una vía urbana con un único carril por sentido de circulación?</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -525,17 +525,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T05</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Relativo a la disposición de la carga en un vehícu</t>
+          <t>Para obedecer esta señal de stop, ¿dónde debe dete</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Relativo a la disposición de la carga en un vehículo, ¿cómo es obligatorio transportar siempre las materias que produzcan polvo o puedan caer?</t>
+          <t>Para obedecer esta señal de stop, ¿dónde debe detenerse si existe suficiente visibilidad?</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -557,65 +557,65 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DGT Junio 26</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>¿Cuál es la velocidad máxima en una vía urbana con</t>
+          <t>Relativo a la disposición de la carga en un vehícu</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>¿Cuál es la velocidad máxima en una vía urbana con un único carril por sentido de circulación?</t>
+          <t>Relativo a la disposición de la carga en un vehículo, ¿cómo es obligatorio transportar siempre las materias que produzcan polvo o puedan caer?</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T4 aje</t>
+          <t>DGT Junio 26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>En caso de avería del alumbrado de corto alcance,</t>
+          <t>¿Qué significa está señal?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>En caso de avería del alumbrado de corto alcance, ¿puede circular fuera de poblado por una vía insuficientemente iluminada con el alumbrado de largo alcance?</t>
+          <t>¿Qué significa está señal?</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H6" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -626,12 +626,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Si no puede alcanzar con su vehículo la velocidad</t>
+          <t>En caso de avería del alumbrado de corto alcance,</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Si no puede alcanzar con su vehículo la velocidad mínima exigida en la vía por la que circula y existe peligro de alcance, ¿qué debe hacer?</t>
+          <t>En caso de avería del alumbrado de corto alcance, ¿puede circular fuera de poblado por una vía insuficientemente iluminada con el alumbrado de largo alcance?</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -658,12 +658,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>La luz antiniebla trasera deberá utilizarse en cas</t>
+          <t>Si no puede alcanzar con su vehículo la velocidad</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>La luz antiniebla trasera deberá utilizarse en caso de...</t>
+          <t>Si no puede alcanzar con su vehículo la velocidad mínima exigida en la vía por la que circula y existe peligro de alcance, ¿qué debe hacer?</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -690,12 +690,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Para no deslumbrar a otros usuarios deberá...</t>
+          <t>La luz antiniebla trasera deberá utilizarse en cas</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Para no deslumbrar a otros usuarios deberá...</t>
+          <t>La luz antiniebla trasera deberá utilizarse en caso de...</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -722,12 +722,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Durante el día, el conductor de un turismo, ¿cuánd</t>
+          <t>Para no deslumbrar a otros usuarios deberá...</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Durante el día, el conductor de un turismo, ¿cuándo está obligado a circular con el alumbrado de corto alcance encendido?</t>
+          <t>Para no deslumbrar a otros usuarios deberá...</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -754,12 +754,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>En condiciones que disminuyen sensiblemente la vis</t>
+          <t>Durante el día, el conductor de un turismo, ¿cuánd</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>En condiciones que disminuyen sensiblemente la visibilidad, como en caso de niebla, ¿está permitido encender solo el alumbrado de posición y el de cruce?</t>
+          <t>Durante el día, el conductor de un turismo, ¿cuándo está obligado a circular con el alumbrado de corto alcance encendido?</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -781,17 +781,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DGT Junio 26</t>
+          <t>T4 aje</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Un turismo, ¿cuándo puede superar la velocidad máx</t>
+          <t>En condiciones que disminuyen sensiblemente la vis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Un turismo, ¿cuándo puede superar la velocidad máxima genérica en 20 km/h?</t>
+          <t>En condiciones que disminuyen sensiblemente la visibilidad, como en caso de niebla, ¿está permitido encender solo el alumbrado de posición y el de cruce?</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -818,12 +818,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Para evitar o retrasar la fatiga, los conductores</t>
+          <t>Un turismo, ¿cuándo puede superar la velocidad máx</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Para evitar o retrasar la fatiga, los conductores deben...</t>
+          <t>Un turismo, ¿cuándo puede superar la velocidad máxima genérica en 20 km/h?</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -850,12 +850,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>La mayoría de los accidentes se deben...</t>
+          <t>Para evitar o retrasar la fatiga, los conductores</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>La mayoría de los accidentes se deben...</t>
+          <t>Para evitar o retrasar la fatiga, los conductores deben...</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -882,12 +882,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Por el carril de alta ocupación VAO, ¿puede circul</t>
+          <t>La mayoría de los accidentes se deben...</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Por el carril de alta ocupación VAO, ¿puede circular un turismo con remolque?</t>
+          <t>La mayoría de los accidentes se deben...</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -914,12 +914,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>En una carretera convencional, ¿está permitido que</t>
+          <t>Por el carril de alta ocupación VAO, ¿puede circul</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>En una carretera convencional, ¿está permitido que un peatón circule por la calzada?</t>
+          <t>Por el carril de alta ocupación VAO, ¿puede circular un turismo con remolque?</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -946,12 +946,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>¿Qué significa está señal?</t>
+          <t>En una carretera convencional, ¿está permitido que</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>¿Qué significa está señal?</t>
+          <t>En una carretera convencional, ¿está permitido que un peatón circule por la calzada?</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -2887,6 +2887,38 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>B Completo revistas</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>4. La vía, su entorno y el propio vehículo, ¿puede</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>4. La vía, su entorno y el propio vehículo, ¿pueden favorecer la aparición de distracciones al volante?</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -603,19 +603,19 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
       <c r="G6" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="H6" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="7">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -603,19 +603,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="H6" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -493,17 +493,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DGT Junio 26</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>¿Cuál es la velocidad máxima en una vía urbana con</t>
+          <t>Para obedecer esta señal de stop, ¿dónde debe dete</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>¿Cuál es la velocidad máxima en una vía urbana con un único carril por sentido de circulación?</t>
+          <t>Para obedecer esta señal de stop, ¿dónde debe detenerse si existe suficiente visibilidad?</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -525,17 +525,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Para obedecer esta señal de stop, ¿dónde debe dete</t>
+          <t>Relativo a la disposición de la carga en un vehícu</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Para obedecer esta señal de stop, ¿dónde debe detenerse si existe suficiente visibilidad?</t>
+          <t>Relativo a la disposición de la carga en un vehículo, ¿cómo es obligatorio transportar siempre las materias que produzcan polvo o puedan caer?</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -557,33 +557,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T05</t>
+          <t>DGT Junio 26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Relativo a la disposición de la carga en un vehícu</t>
+          <t>¿Cuál es la velocidad máxima en una vía urbana con</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Relativo a la disposición de la carga en un vehículo, ¿cómo es obligatorio transportar siempre las materias que produzcan polvo o puedan caer?</t>
+          <t>¿Cuál es la velocidad máxima en una vía urbana con un único carril por sentido de circulación?</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -603,19 +603,19 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="H6" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="7">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="H5" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="6">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2922,6 +2922,38 @@
         <v>100</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>B Completo revistas</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>21. La carga transportada en un vehículo, debe est</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>21. La carga transportada en un vehículo, debe estar dispuesta de forma que...</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2954,6 +2954,38 @@
         <v>100</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>B Completo revistas</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>26. Si el vehículo de detrás se acerca demasiado,</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>26. Si el vehículo de detrás se acerca demasiado, es conveniente...</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -2962,12 +2962,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>26. Si el vehículo de detrás se acerca demasiado,</t>
+          <t>2. Para que pueda circular un ciclomotor, ¿es obli</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>26. Si el vehículo de detrás se acerca demasiado, es conveniente...</t>
+          <t>2. Para que pueda circular un ciclomotor, ¿es obligatorio que esté asegurado?</t>
         </is>
       </c>
       <c r="D80" t="n">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2. Para que pueda circular un ciclomotor, ¿es obli</t>
+          <t>26. Si el vehículo de detrás se acerca demasiado,</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2. Para que pueda circular un ciclomotor, ¿es obligatorio que esté asegurado?</t>
+          <t>26. Si el vehículo de detrás se acerca demasiado, es conveniente...</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -2983,6 +2983,38 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>B Completo revistas</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>29. Al adelantar a un peatón, es obligatorio dejar</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>29. Al adelantar a un peatón, es obligatorio dejar una separación lateral mínima de 1,50 metros cuando circule...</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3018,6 +3018,38 @@
         <v>100</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>B Completo revistas</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>14. ¿Cuándo debe comprobar el reglaje de los espej</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>14. ¿Cuándo debe comprobar el reglaje de los espejos retrovisores?</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -603,19 +603,19 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
         <v>3</v>
       </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="H6" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
         <v>3</v>
       </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="H5" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -603,19 +603,19 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
         <v>4</v>
       </c>
-      <c r="E6" t="n">
-        <v>3</v>
-      </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H6" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
         <v>4</v>
       </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H5" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -562,12 +562,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>¿Cuál es la velocidad máxima en una vía urbana con</t>
+          <t>¿Qué significa está señal?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>¿Cuál es la velocidad máxima en una vía urbana con un único carril por sentido de circulación?</t>
+          <t>¿Qué significa está señal?</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -594,28 +594,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>¿Qué significa está señal?</t>
+          <t>¿Cuál es la velocidad máxima en una vía urbana con</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>¿Qué significa está señal?</t>
+          <t>¿Cuál es la velocidad máxima en una vía urbana con un único carril por sentido de circulación?</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="n">
-        <v>4</v>
-      </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="H6" t="n">
-        <v>80</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="7">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -571,19 +571,19 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="n">
-        <v>4</v>
-      </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="H5" t="n">
-        <v>80</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="6">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,10 +449,15 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>aciertos_consecutivos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>porcentaje_fallos</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>porcentaje_aciertos</t>
         </is>
@@ -484,9 +489,12 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
+        <v>100</v>
+      </c>
+      <c r="I2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -516,9 +524,12 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -548,9 +559,12 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
+        <v>100</v>
+      </c>
+      <c r="I4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -580,9 +594,12 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>16.7</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>83.3</v>
       </c>
     </row>
@@ -603,19 +620,22 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
         <v>6</v>
       </c>
-      <c r="E6" t="n">
-        <v>5</v>
-      </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>16.7</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>83.3</v>
+        <v>14.3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>85.7</v>
       </c>
     </row>
     <row r="7">
@@ -647,6 +667,9 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
         <v>100</v>
       </c>
     </row>
@@ -679,6 +702,9 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
         <v>100</v>
       </c>
     </row>
@@ -711,6 +737,9 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>100</v>
       </c>
     </row>
@@ -743,6 +772,9 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>100</v>
       </c>
     </row>
@@ -775,6 +807,9 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>100</v>
       </c>
     </row>
@@ -807,6 +842,9 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>100</v>
       </c>
     </row>
@@ -839,6 +877,9 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>100</v>
       </c>
     </row>
@@ -871,6 +912,9 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
         <v>100</v>
       </c>
     </row>
@@ -903,6 +947,9 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>100</v>
       </c>
     </row>
@@ -935,6 +982,9 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>100</v>
       </c>
     </row>
@@ -967,6 +1017,9 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>100</v>
       </c>
     </row>
@@ -999,6 +1052,9 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1031,6 +1087,9 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1063,6 +1122,9 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1095,6 +1157,9 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1127,6 +1192,9 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1159,6 +1227,9 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1191,6 +1262,9 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1223,6 +1297,9 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1255,6 +1332,9 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1287,6 +1367,9 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1319,6 +1402,9 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1351,6 +1437,9 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1383,6 +1472,9 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1415,6 +1507,9 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1447,6 +1542,9 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1479,6 +1577,9 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1511,6 +1612,9 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1543,6 +1647,9 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1575,6 +1682,9 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1607,6 +1717,9 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1639,6 +1752,9 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1671,6 +1787,9 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1703,6 +1822,9 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1735,6 +1857,9 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1767,6 +1892,9 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1799,6 +1927,9 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1831,6 +1962,9 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1863,6 +1997,9 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1895,6 +2032,9 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1927,6 +2067,9 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1959,6 +2102,9 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
         <v>100</v>
       </c>
     </row>
@@ -1991,6 +2137,9 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2023,6 +2172,9 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2055,6 +2207,9 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2087,6 +2242,9 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2119,6 +2277,9 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2151,6 +2312,9 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2183,6 +2347,9 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2215,6 +2382,9 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2247,6 +2417,9 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2279,6 +2452,9 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2311,6 +2487,9 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2343,6 +2522,9 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2375,6 +2557,9 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2407,6 +2592,9 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2439,6 +2627,9 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2471,6 +2662,9 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2503,6 +2697,9 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2535,6 +2732,9 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2567,6 +2767,9 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2599,6 +2802,9 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2631,6 +2837,9 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2663,6 +2872,9 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2695,6 +2907,9 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2727,6 +2942,9 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2759,6 +2977,9 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2791,6 +3012,9 @@
         <v>0</v>
       </c>
       <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2823,6 +3047,9 @@
         <v>0</v>
       </c>
       <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2855,6 +3082,9 @@
         <v>0</v>
       </c>
       <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2887,6 +3117,9 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2919,6 +3152,9 @@
         <v>0</v>
       </c>
       <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2951,6 +3187,9 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2983,6 +3222,9 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
         <v>100</v>
       </c>
     </row>
@@ -3015,6 +3257,9 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
         <v>100</v>
       </c>
     </row>
@@ -3047,6 +3292,9 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="n">
         <v>6</v>
       </c>
-      <c r="E5" t="n">
-        <v>5</v>
-      </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="I5" t="n">
-        <v>83.3</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="6">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -620,22 +620,22 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
         <v>7</v>
       </c>
-      <c r="E6" t="n">
-        <v>6</v>
-      </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>14.3</v>
+        <v>12.5</v>
       </c>
       <c r="I6" t="n">
-        <v>85.7</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="7">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -466,27 +466,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DGT Junio 26</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>¿Pueden las motocicletas llevar la luz antiniebla</t>
+          <t>Relativo a la disposición de la carga en un vehícu</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>¿Pueden las motocicletas llevar la luz antiniebla delantera?</t>
+          <t>Relativo a la disposición de la carga en un vehículo, ¿cómo es obligatorio transportar siempre las materias que produzcan polvo o puedan caer?</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -501,17 +501,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>DGT Junio 26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Para obedecer esta señal de stop, ¿dónde debe dete</t>
+          <t>¿Pueden las motocicletas llevar la luz antiniebla</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Para obedecer esta señal de stop, ¿dónde debe detenerse si existe suficiente visibilidad?</t>
+          <t>¿Pueden las motocicletas llevar la luz antiniebla delantera?</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -536,17 +536,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T05</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Relativo a la disposición de la carga en un vehícu</t>
+          <t>Para obedecer esta señal de stop, ¿dónde debe dete</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Relativo a la disposición de la carga en un vehículo, ¿cómo es obligatorio transportar siempre las materias que produzcan polvo o puedan caer?</t>
+          <t>Para obedecer esta señal de stop, ¿dónde debe detenerse si existe suficiente visibilidad?</t>
         </is>
       </c>
       <c r="D4" t="n">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -466,27 +466,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T05</t>
+          <t>DGT Junio 26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Relativo a la disposición de la carga en un vehícu</t>
+          <t>¿Pueden las motocicletas llevar la luz antiniebla</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Relativo a la disposición de la carga en un vehículo, ¿cómo es obligatorio transportar siempre las materias que produzcan polvo o puedan caer?</t>
+          <t>¿Pueden las motocicletas llevar la luz antiniebla delantera?</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -501,17 +501,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DGT Junio 26</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>¿Pueden las motocicletas llevar la luz antiniebla</t>
+          <t>Relativo a la disposición de la carga en un vehícu</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>¿Pueden las motocicletas llevar la luz antiniebla delantera?</t>
+          <t>Relativo a la disposición de la carga en un vehículo, ¿cómo es obligatorio transportar siempre las materias que produzcan polvo o puedan caer?</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -550,22 +550,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="n">
         <v>7</v>
       </c>
-      <c r="E5" t="n">
-        <v>6</v>
-      </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>14.3</v>
+        <v>12.5</v>
       </c>
       <c r="I5" t="n">
-        <v>85.7</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="6">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -466,27 +466,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DGT Junio 26</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>¿Pueden las motocicletas llevar la luz antiniebla</t>
+          <t>Relativo a la disposición de la carga en un vehícu</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>¿Pueden las motocicletas llevar la luz antiniebla delantera?</t>
+          <t>Relativo a la disposición de la carga en un vehículo, ¿cómo es obligatorio transportar siempre las materias que produzcan polvo o puedan caer?</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -501,17 +501,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T05</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Relativo a la disposición de la carga en un vehícu</t>
+          <t>Para obedecer esta señal de stop, ¿dónde debe dete</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Relativo a la disposición de la carga en un vehículo, ¿cómo es obligatorio transportar siempre las materias que produzcan polvo o puedan caer?</t>
+          <t>Para obedecer esta señal de stop, ¿dónde debe detenerse si existe suficiente visibilidad?</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -536,17 +536,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>DGT Junio 26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Para obedecer esta señal de stop, ¿dónde debe dete</t>
+          <t>¿Pueden las motocicletas llevar la luz antiniebla</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Para obedecer esta señal de stop, ¿dónde debe detenerse si existe suficiente visibilidad?</t>
+          <t>¿Pueden las motocicletas llevar la luz antiniebla delantera?</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>12.5</v>
+        <v>14.3</v>
       </c>
       <c r="I5" t="n">
-        <v>87.5</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="6">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -620,22 +620,22 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" t="n">
         <v>8</v>
       </c>
-      <c r="E6" t="n">
-        <v>7</v>
-      </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="I6" t="n">
-        <v>87.5</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="7">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -480,13 +480,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -515,22 +515,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -550,22 +550,22 @@
         </is>
       </c>
       <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="I4" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="5">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E5" t="n">
         <v>8</v>
       </c>
-      <c r="E5" t="n">
-        <v>7</v>
-      </c>
       <c r="F5" t="n">
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="I5" t="n">
-        <v>87.5</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="6">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -480,22 +480,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -480,22 +480,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -515,22 +515,22 @@
         </is>
       </c>
       <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
         <v>2</v>
       </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="I3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="4">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -550,22 +550,22 @@
         </is>
       </c>
       <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="I4" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -576,12 +576,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>¿Qué significa está señal?</t>
+          <t>¿Cuál es la velocidad máxima en una vía urbana con</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>¿Qué significa está señal?</t>
+          <t>¿Cuál es la velocidad máxima en una vía urbana con un único carril por sentido de circulación?</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -611,31 +611,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>¿Cuál es la velocidad máxima en una vía urbana con</t>
+          <t>¿Qué significa está señal?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>¿Cuál es la velocidad máxima en una vía urbana con un único carril por sentido de circulación?</t>
+          <t>¿Qué significa está señal?</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
         <v>9</v>
       </c>
-      <c r="E6" t="n">
-        <v>8</v>
-      </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="I6" t="n">
-        <v>88.90000000000001</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -515,22 +515,22 @@
         </is>
       </c>
       <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
         <v>3</v>
       </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="I3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -515,22 +515,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>25</v>
+        <v>33.3</v>
       </c>
       <c r="I3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="4">
@@ -550,22 +550,22 @@
         </is>
       </c>
       <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
         <v>4</v>
       </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I4" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -515,22 +515,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="I3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -480,22 +480,22 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
         <v>4</v>
       </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3</v>
-      </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -480,22 +480,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -515,22 +515,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -515,22 +515,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -480,22 +480,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="I2" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="3">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -515,22 +515,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="I3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="4">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -480,22 +480,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
         <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="I2" t="n">
-        <v>33.3</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="3">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3298,6 +3298,41 @@
         <v>100</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>En este tramo de vía, ¿cuál es la velocidad máxima</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>En este tramo de vía, ¿cuál es la velocidad máxima?</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3333,6 +3333,41 @@
         <v>100</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Esta señalización, le indica la distancia...</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Esta señalización, le indica la distancia...</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3368,6 +3368,41 @@
         <v>100</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>¿Qué indica lamarca de color blanco de la derecha?</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>¿Qué indica lamarca de color blanco de la derecha?</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3341,12 +3341,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Esta señalización, le indica la distancia...</t>
+          <t>Si un conductor se encuentra esta señal, debe sabe</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Esta señalización, le indica la distancia...</t>
+          <t>Si un conductor se encuentra esta señal, debe saber que en la próxima intersección...</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3365,41 +3365,6 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>T03</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>¿Qué indica lamarca de color blanco de la derecha?</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>¿Qué indica lamarca de color blanco de la derecha?</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" t="n">
-        <v>1</v>
-      </c>
-      <c r="F85" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" t="n">
-        <v>1</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3341,12 +3341,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Si un conductor se encuentra esta señal, debe sabe</t>
+          <t>Esta señalización, le indica la distancia...</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Si un conductor se encuentra esta señal, debe saber que en la próxima intersección...</t>
+          <t>Esta señalización, le indica la distancia...</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3365,6 +3365,76 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>¿Qué indica lamarca de color blanco de la derecha?</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>¿Qué indica lamarca de color blanco de la derecha?</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>La señal...</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>La señal...</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3438,6 +3438,41 @@
         <v>100</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>En esta intersección con un semáforo en amarillo i</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>En esta intersección con un semáforo en amarillo intermitente, ¿qué debe hacer?</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3473,6 +3473,41 @@
         <v>100</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>¿Qué indica esta señal?</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>¿Qué indica esta señal?</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -3481,12 +3481,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>¿Qué indica esta señal?</t>
+          <t>A partir de esta señal, ¿puede adelantar?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>¿Qué indica esta señal?</t>
+          <t>A partir de esta señal, ¿puede adelantar?</t>
         </is>
       </c>
       <c r="D88" t="n">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I88"/>
+  <dimension ref="A1:I89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3508,6 +3508,41 @@
         <v>100</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>A la vista de la imagen, el conductor del vehículo</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>A la vista de la imagen, el conductor del vehículo amarillo, ¿está obligado siempre a detenerse?</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -3481,12 +3481,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>A partir de esta señal, ¿puede adelantar?</t>
+          <t>¿Qué indica esta señal?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>A partir de esta señal, ¿puede adelantar?</t>
+          <t>¿Qué indica esta señal?</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>A la vista de la imagen, el conductor del vehículo</t>
+          <t>Una marca longitudinal formada por dos líneas cont</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>A la vista de la imagen, el conductor del vehículo amarillo, ¿está obligado siempre a detenerse?</t>
+          <t>Una marca longitudinal formada por dos líneas continuas adosadas...</t>
         </is>
       </c>
       <c r="D89" t="n">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,6 +495,41 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>El consumo de alcohol, ¿deteriora las capacidades</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>El consumo de alcohol, ¿deteriora las capacidades para conducir con seguridad?</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -515,16 +515,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,6 +530,41 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Circula por un carril y sobre él encuentra un semá</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Circula por un carril y sobre él encuentra un semáforo con una luz roja en forma de aspa; ¿qué debe hacer?</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,6 +565,41 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Si conduce una motocicleta con un pasajero, ¿qué d</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Si conduce una motocicleta con un pasajero, ¿qué debe tener en cuenta?</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,6 +600,41 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cuando el vehículo amarillo gire a la derecha, ¿qu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Cuando el vehículo amarillo gire a la derecha, ¿qué debe hacer el conductor del vehículo verde?</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -466,65 +466,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T05</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Transporta en su turismo una carga que sobresale p</t>
+          <t>¿Qué le indica la señal?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Transporta en su turismo una carga que sobresale por la parte trasera, ¿debe señalizarla si circula de día?</t>
+          <t>¿Qué le indica la señal?</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>El consumo de alcohol, ¿deteriora las capacidades</t>
+          <t>Transporta en su turismo una carga que sobresale p</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>El consumo de alcohol, ¿deteriora las capacidades para conducir con seguridad?</t>
+          <t>Transporta en su turismo una carga que sobresale por la parte trasera, ¿debe señalizarla si circula de día?</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -536,30 +536,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Circula por un carril y sobre él encuentra un semá</t>
+          <t>El consumo de alcohol, ¿deteriora las capacidades</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Circula por un carril y sobre él encuentra un semáforo con una luz roja en forma de aspa; ¿qué debe hacer?</t>
+          <t>El consumo de alcohol, ¿deteriora las capacidades para conducir con seguridad?</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -571,17 +571,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Si conduce una motocicleta con un pasajero, ¿qué d</t>
+          <t>Circula por un carril y sobre él encuentra un semá</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Si conduce una motocicleta con un pasajero, ¿qué debe tener en cuenta?</t>
+          <t>Circula por un carril y sobre él encuentra un semáforo con una luz roja en forma de aspa; ¿qué debe hacer?</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -606,17 +606,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cuando el vehículo amarillo gire a la derecha, ¿qu</t>
+          <t>Si conduce una motocicleta con un pasajero, ¿qué d</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cuando el vehículo amarillo gire a la derecha, ¿qué debe hacer el conductor del vehículo verde?</t>
+          <t>Si conduce una motocicleta con un pasajero, ¿qué debe tener en cuenta?</t>
         </is>
       </c>
       <c r="D6" t="n">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -635,6 +635,41 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Circular por debajo de la velocidad mínima permiti</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Circular por debajo de la velocidad mínima permitida, ¿podría ser un factor de riesgo?</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -466,65 +466,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>¿Qué le indica la señal?</t>
+          <t>Transporta en su turismo una carga que sobresale p</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>¿Qué le indica la señal?</t>
+          <t>Transporta en su turismo una carga que sobresale por la parte trasera, ¿debe señalizarla si circula de día?</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>100</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T05</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Transporta en su turismo una carga que sobresale p</t>
+          <t>El consumo de alcohol, ¿deteriora las capacidades</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Transporta en su turismo una carga que sobresale por la parte trasera, ¿debe señalizarla si circula de día?</t>
+          <t>El consumo de alcohol, ¿deteriora las capacidades para conducir con seguridad?</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -536,30 +536,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>El consumo de alcohol, ¿deteriora las capacidades</t>
+          <t>Circula por un carril y sobre él encuentra un semá</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>El consumo de alcohol, ¿deteriora las capacidades para conducir con seguridad?</t>
+          <t>Circula por un carril y sobre él encuentra un semáforo con una luz roja en forma de aspa; ¿qué debe hacer?</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -571,17 +571,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Circula por un carril y sobre él encuentra un semá</t>
+          <t>Si conduce una motocicleta con un pasajero, ¿qué d</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Circula por un carril y sobre él encuentra un semáforo con una luz roja en forma de aspa; ¿qué debe hacer?</t>
+          <t>Si conduce una motocicleta con un pasajero, ¿qué debe tener en cuenta?</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -606,17 +606,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Si conduce una motocicleta con un pasajero, ¿qué d</t>
+          <t>Cuando el vehículo amarillo gire a la derecha, ¿qu</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Si conduce una motocicleta con un pasajero, ¿qué debe tener en cuenta?</t>
+          <t>Cuando el vehículo amarillo gire a la derecha, ¿qué debe hacer el conductor del vehículo verde?</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -641,17 +641,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Circular por debajo de la velocidad mínima permiti</t>
+          <t>Puede circular con su turismo si el equipaje no pe</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Circular por debajo de la velocidad mínima permitida, ¿podría ser un factor de riesgo?</t>
+          <t>Puede circular con su turismo si el equipaje no permite la visión adecuada de la vía por el espejo retrovisor interior?</t>
         </is>
       </c>
       <c r="D7" t="n">

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,65 +466,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T05</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Transporta en su turismo una carga que sobresale p</t>
+          <t>¿Qué le indica la señal?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Transporta en su turismo una carga que sobresale por la parte trasera, ¿debe señalizarla si circula de día?</t>
+          <t>¿Qué le indica la señal?</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>El consumo de alcohol, ¿deteriora las capacidades</t>
+          <t>Transporta en su turismo una carga que sobresale p</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>El consumo de alcohol, ¿deteriora las capacidades para conducir con seguridad?</t>
+          <t>Transporta en su turismo una carga que sobresale por la parte trasera, ¿debe señalizarla si circula de día?</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -536,30 +536,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Circula por un carril y sobre él encuentra un semá</t>
+          <t>El consumo de alcohol, ¿deteriora las capacidades</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Circula por un carril y sobre él encuentra un semáforo con una luz roja en forma de aspa; ¿qué debe hacer?</t>
+          <t>El consumo de alcohol, ¿deteriora las capacidades para conducir con seguridad?</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -571,17 +571,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Si conduce una motocicleta con un pasajero, ¿qué d</t>
+          <t>Circula por un carril y sobre él encuentra un semá</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Si conduce una motocicleta con un pasajero, ¿qué debe tener en cuenta?</t>
+          <t>Circula por un carril y sobre él encuentra un semáforo con una luz roja en forma de aspa; ¿qué debe hacer?</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -606,17 +606,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cuando el vehículo amarillo gire a la derecha, ¿qu</t>
+          <t>Si conduce una motocicleta con un pasajero, ¿qué d</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cuando el vehículo amarillo gire a la derecha, ¿qué debe hacer el conductor del vehículo verde?</t>
+          <t>Si conduce una motocicleta con un pasajero, ¿qué debe tener en cuenta?</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -641,17 +641,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T02</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Puede circular con su turismo si el equipaje no pe</t>
+          <t>Circular por debajo de la velocidad mínima permiti</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Puede circular con su turismo si el equipaje no permite la visión adecuada de la vía por el espejo retrovisor interior?</t>
+          <t>Circular por debajo de la velocidad mínima permitida, ¿podría ser un factor de riesgo?</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -670,6 +670,41 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>El calor excesivo en el interior del vehículo, ¿pu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>El calor excesivo en el interior del vehículo, ¿puede aumentar el riesgo en la conducción?</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -708,6 +708,41 @@
         <v>100</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>¿Cómo debe colocar el navegador GPS portátil en el</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>¿Cómo debe colocar el navegador GPS portátil en el vehículo?</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,65 +466,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>¿Qué le indica la señal?</t>
+          <t>Transporta en su turismo una carga que sobresale p</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>¿Qué le indica la señal?</t>
+          <t>Transporta en su turismo una carga que sobresale por la parte trasera, ¿debe señalizarla si circula de día?</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>100</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T05</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Transporta en su turismo una carga que sobresale p</t>
+          <t>El consumo de alcohol, ¿deteriora las capacidades</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Transporta en su turismo una carga que sobresale por la parte trasera, ¿debe señalizarla si circula de día?</t>
+          <t>El consumo de alcohol, ¿deteriora las capacidades para conducir con seguridad?</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -536,30 +536,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>El consumo de alcohol, ¿deteriora las capacidades</t>
+          <t>Circula por un carril y sobre él encuentra un semá</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>El consumo de alcohol, ¿deteriora las capacidades para conducir con seguridad?</t>
+          <t>Circula por un carril y sobre él encuentra un semáforo con una luz roja en forma de aspa; ¿qué debe hacer?</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -571,17 +571,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Circula por un carril y sobre él encuentra un semá</t>
+          <t>Si conduce una motocicleta con un pasajero, ¿qué d</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Circula por un carril y sobre él encuentra un semáforo con una luz roja en forma de aspa; ¿qué debe hacer?</t>
+          <t>Si conduce una motocicleta con un pasajero, ¿qué debe tener en cuenta?</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -606,17 +606,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Si conduce una motocicleta con un pasajero, ¿qué d</t>
+          <t>Cuando el vehículo amarillo gire a la derecha, ¿qu</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Si conduce una motocicleta con un pasajero, ¿qué debe tener en cuenta?</t>
+          <t>Cuando el vehículo amarillo gire a la derecha, ¿qué debe hacer el conductor del vehículo verde?</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -641,17 +641,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Circular por debajo de la velocidad mínima permiti</t>
+          <t>Puede circular con su turismo si el equipaje no pe</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Circular por debajo de la velocidad mínima permitida, ¿podría ser un factor de riesgo?</t>
+          <t>Puede circular con su turismo si el equipaje no permite la visión adecuada de la vía por el espejo retrovisor interior?</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -681,12 +681,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>El calor excesivo en el interior del vehículo, ¿pu</t>
+          <t>La velocidad, ¿es un factor de riesgo que produce</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>El calor excesivo en el interior del vehículo, ¿puede aumentar el riesgo en la conducción?</t>
+          <t>La velocidad, ¿es un factor de riesgo que produce accidentes?</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -705,41 +705,6 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>T07</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>¿Cómo debe colocar el navegador GPS portátil en el</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>¿Cómo debe colocar el navegador GPS portátil en el vehículo?</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,65 +466,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T05</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Transporta en su turismo una carga que sobresale p</t>
+          <t>¿Qué le indica la señal?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Transporta en su turismo una carga que sobresale por la parte trasera, ¿debe señalizarla si circula de día?</t>
+          <t>¿Qué le indica la señal?</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>El consumo de alcohol, ¿deteriora las capacidades</t>
+          <t>Transporta en su turismo una carga que sobresale p</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>El consumo de alcohol, ¿deteriora las capacidades para conducir con seguridad?</t>
+          <t>Transporta en su turismo una carga que sobresale por la parte trasera, ¿debe señalizarla si circula de día?</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -536,30 +536,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Circula por un carril y sobre él encuentra un semá</t>
+          <t>El consumo de alcohol, ¿deteriora las capacidades</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Circula por un carril y sobre él encuentra un semáforo con una luz roja en forma de aspa; ¿qué debe hacer?</t>
+          <t>El consumo de alcohol, ¿deteriora las capacidades para conducir con seguridad?</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -571,17 +571,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Si conduce una motocicleta con un pasajero, ¿qué d</t>
+          <t>Circula por un carril y sobre él encuentra un semá</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Si conduce una motocicleta con un pasajero, ¿qué debe tener en cuenta?</t>
+          <t>Circula por un carril y sobre él encuentra un semáforo con una luz roja en forma de aspa; ¿qué debe hacer?</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -606,17 +606,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cuando el vehículo amarillo gire a la derecha, ¿qu</t>
+          <t>Si conduce una motocicleta con un pasajero, ¿qué d</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cuando el vehículo amarillo gire a la derecha, ¿qué debe hacer el conductor del vehículo verde?</t>
+          <t>Si conduce una motocicleta con un pasajero, ¿qué debe tener en cuenta?</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -641,17 +641,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T02</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Puede circular con su turismo si el equipaje no pe</t>
+          <t>Circular por debajo de la velocidad mínima permiti</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Puede circular con su turismo si el equipaje no permite la visión adecuada de la vía por el espejo retrovisor interior?</t>
+          <t>Circular por debajo de la velocidad mínima permitida, ¿podría ser un factor de riesgo?</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -681,12 +681,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>La velocidad, ¿es un factor de riesgo que produce</t>
+          <t>El calor excesivo en el interior del vehículo, ¿pu</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>La velocidad, ¿es un factor de riesgo que produce accidentes?</t>
+          <t>El calor excesivo en el interior del vehículo, ¿puede aumentar el riesgo en la conducción?</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -705,6 +705,76 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>¿Cómo debe colocar el navegador GPS portátil en el</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>¿Cómo debe colocar el navegador GPS portátil en el vehículo?</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>T01 Uso vias públicas</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Si los ocupantes de los asientos traseros de un ve</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Si los ocupantes de los asientos traseros de un vehículo son menores de edad y de estatura igual o inferior a 135 cm de altura, ¿qué dispositivos de seguridad deben utilizar?</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,6 +778,41 @@
         <v>100</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>De los siguientes, ¿qué grupos tienen una mayor pr</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>De los siguientes, ¿qué grupos tienen una mayor probabilidad de sufrir un accidente de tráfico como peatones?</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -813,6 +813,41 @@
         <v>100</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T10 TECNICAS COND</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mientras conduce, ¿es aconsejable utilizar los esp</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Mientras conduce, ¿es aconsejable utilizar los espejos retrovisores con regularidad?</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>De los siguientes, ¿qué grupos tienen una mayor pr</t>
+          <t>Entre los factores que favorecen la aparición de l</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>De los siguientes, ¿qué grupos tienen una mayor probabilidad de sufrir un accidente de tráfico como peatones?</t>
+          <t>Entre los factores que favorecen la aparición de la fatiga en el conductor se encuentra:</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -810,41 +810,6 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>T10 TECNICAS COND</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Mientras conduce, ¿es aconsejable utilizar los esp</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Mientras conduce, ¿es aconsejable utilizar los espejos retrovisores con regularidad?</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Entre los factores que favorecen la aparición de l</t>
+          <t>De los siguientes, ¿qué grupos tienen una mayor pr</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Entre los factores que favorecen la aparición de la fatiga en el conductor se encuentra:</t>
+          <t>De los siguientes, ¿qué grupos tienen una mayor probabilidad de sufrir un accidente de tráfico como peatones?</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -810,6 +810,76 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T10 TECNICAS COND</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mientras conduce, ¿es aconsejable utilizar los esp</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Mientras conduce, ¿es aconsejable utilizar los espejos retrovisores con regularidad?</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>En una intersección, un conductor que se acerque d</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>En una intersección, un conductor que se acerque de frente a un agente de tráfico que tenga el brazo levantado verticalmente, deberá detener su vehículo...</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -883,6 +883,41 @@
         <v>100</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>¿Tiene usted que ceder el paso al vehículo que se</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>¿Tiene usted que ceder el paso al vehículo que se incorpora a la circulación?</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>De los siguientes, ¿qué grupos tienen una mayor pr</t>
+          <t>Entre los factores que favorecen la aparición de l</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>De los siguientes, ¿qué grupos tienen una mayor probabilidad de sufrir un accidente de tráfico como peatones?</t>
+          <t>Entre los factores que favorecen la aparición de la fatiga en el conductor se encuentra:</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -816,17 +816,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T10 TECNICAS COND</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mientras conduce, ¿es aconsejable utilizar los esp</t>
+          <t>Es aconsejable evitar las comidas copiosas si se v</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mientras conduce, ¿es aconsejable utilizar los espejos retrovisores con regularidad?</t>
+          <t>Es aconsejable evitar las comidas copiosas si se va a conducir un vehículo ya que, en general, suelen producir...</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -845,76 +845,6 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>T02</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>En una intersección, un conductor que se acerque d</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>En una intersección, un conductor que se acerque de frente a un agente de tráfico que tenga el brazo levantado verticalmente, deberá detener su vehículo...</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>T02</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>¿Tiene usted que ceder el paso al vehículo que se</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>¿Tiene usted que ceder el paso al vehículo que se incorpora a la circulación?</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Entre los factores que favorecen la aparición de l</t>
+          <t>De los siguientes, ¿qué grupos tienen una mayor pr</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Entre los factores que favorecen la aparición de la fatiga en el conductor se encuentra:</t>
+          <t>De los siguientes, ¿qué grupos tienen una mayor probabilidad de sufrir un accidente de tráfico como peatones?</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -816,17 +816,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T10 TECNICAS COND</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Es aconsejable evitar las comidas copiosas si se v</t>
+          <t>Mientras conduce, ¿es aconsejable utilizar los esp</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Es aconsejable evitar las comidas copiosas si se va a conducir un vehículo ya que, en general, suelen producir...</t>
+          <t>Mientras conduce, ¿es aconsejable utilizar los espejos retrovisores con regularidad?</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -845,6 +845,111 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>En una intersección, un conductor que se acerque d</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>En una intersección, un conductor que se acerque de frente a un agente de tráfico que tenga el brazo levantado verticalmente, deberá detener su vehículo...</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>¿Tiene usted que ceder el paso al vehículo que se</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>¿Tiene usted que ceder el paso al vehículo que se incorpora a la circulación?</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>El titular de un permiso A, ¿puede conducir motoci</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>El titular de un permiso A, ¿puede conducir motocicletas con sidecar?</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -953,6 +953,41 @@
         <v>100</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>En la situación de la fotografía, el conductor del</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>En la situación de la fotografía, el conductor del camión, ¿está obligado a apartarse al arcén para facilitar el adelantamiento a otros vehículos?</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>De los siguientes, ¿qué grupos tienen una mayor pr</t>
+          <t>Entre los factores que favorecen la aparición de l</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>De los siguientes, ¿qué grupos tienen una mayor probabilidad de sufrir un accidente de tráfico como peatones?</t>
+          <t>Entre los factores que favorecen la aparición de la fatiga en el conductor se encuentra:</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -816,17 +816,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T10 TECNICAS COND</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mientras conduce, ¿es aconsejable utilizar los esp</t>
+          <t>Es aconsejable evitar las comidas copiosas si se v</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mientras conduce, ¿es aconsejable utilizar los espejos retrovisores con regularidad?</t>
+          <t>Es aconsejable evitar las comidas copiosas si se va a conducir un vehículo ya que, en general, suelen producir...</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -851,17 +851,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T02</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>En una intersección, un conductor que se acerque d</t>
+          <t>Si vamos a realizar un desplazamiento largo, para</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>En una intersección, un conductor que se acerque de frente a un agente de tráfico que tenga el brazo levantado verticalmente, deberá detener su vehículo...</t>
+          <t>Si vamos a realizar un desplazamiento largo, para reducir la posibilidad de aparición de la somnolencia durante la conducción es aconsejable...</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -880,111 +880,6 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>T02</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>¿Tiene usted que ceder el paso al vehículo que se</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>¿Tiene usted que ceder el paso al vehículo que se incorpora a la circulación?</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>T06</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>El titular de un permiso A, ¿puede conducir motoci</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>El titular de un permiso A, ¿puede conducir motocicletas con sidecar?</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>T02</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>En la situación de la fotografía, el conductor del</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>En la situación de la fotografía, el conductor del camión, ¿está obligado a apartarse al arcén para facilitar el adelantamiento a otros vehículos?</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -883,6 +883,41 @@
         <v>100</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T10 TECNICAS COND</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Si se modifica la aerodinámica del vehículo añadie</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Si se modifica la aerodinámica del vehículo añadiendo elementos para hacerlo más atractivo...</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,65 +501,65 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T05</t>
+          <t>T02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Transporta en su turismo una carga que sobresale p</t>
+          <t>¿Puede adelantar por la derecha al vehículo rojo?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Transporta en su turismo una carga que sobresale por la parte trasera, ¿debe señalizarla si circula de día?</t>
+          <t>¿Puede adelantar por la derecha al vehículo rojo?</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>El consumo de alcohol, ¿deteriora las capacidades</t>
+          <t>Transporta en su turismo una carga que sobresale p</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>El consumo de alcohol, ¿deteriora las capacidades para conducir con seguridad?</t>
+          <t>Transporta en su turismo una carga que sobresale por la parte trasera, ¿debe señalizarla si circula de día?</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -571,30 +571,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Circula por un carril y sobre él encuentra un semá</t>
+          <t>El consumo de alcohol, ¿deteriora las capacidades</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Circula por un carril y sobre él encuentra un semáforo con una luz roja en forma de aspa; ¿qué debe hacer?</t>
+          <t>El consumo de alcohol, ¿deteriora las capacidades para conducir con seguridad?</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -606,17 +606,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Si conduce una motocicleta con un pasajero, ¿qué d</t>
+          <t>Circula por un carril y sobre él encuentra un semá</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Si conduce una motocicleta con un pasajero, ¿qué debe tener en cuenta?</t>
+          <t>Circula por un carril y sobre él encuentra un semáforo con una luz roja en forma de aspa; ¿qué debe hacer?</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -646,12 +646,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Circular por debajo de la velocidad mínima permiti</t>
+          <t>Si conduce una motocicleta con un pasajero, ¿qué d</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Circular por debajo de la velocidad mínima permitida, ¿podría ser un factor de riesgo?</t>
+          <t>Si conduce una motocicleta con un pasajero, ¿qué debe tener en cuenta?</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -681,12 +681,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>El calor excesivo en el interior del vehículo, ¿pu</t>
+          <t>Circular por debajo de la velocidad mínima permiti</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>El calor excesivo en el interior del vehículo, ¿puede aumentar el riesgo en la conducción?</t>
+          <t>Circular por debajo de la velocidad mínima permitida, ¿podría ser un factor de riesgo?</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -716,12 +716,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>¿Cómo debe colocar el navegador GPS portátil en el</t>
+          <t>El calor excesivo en el interior del vehículo, ¿pu</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>¿Cómo debe colocar el navegador GPS portátil en el vehículo?</t>
+          <t>El calor excesivo en el interior del vehículo, ¿puede aumentar el riesgo en la conducción?</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -746,17 +746,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T01 Uso vias públicas</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Si los ocupantes de los asientos traseros de un ve</t>
+          <t>¿Cómo debe colocar el navegador GPS portátil en el</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Si los ocupantes de los asientos traseros de un vehículo son menores de edad y de estatura igual o inferior a 135 cm de altura, ¿qué dispositivos de seguridad deben utilizar?</t>
+          <t>¿Cómo debe colocar el navegador GPS portátil en el vehículo?</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -781,17 +781,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T01 Uso vias públicas</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Entre los factores que favorecen la aparición de l</t>
+          <t>Si los ocupantes de los asientos traseros de un ve</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Entre los factores que favorecen la aparición de la fatiga en el conductor se encuentra:</t>
+          <t>Si los ocupantes de los asientos traseros de un vehículo son menores de edad y de estatura igual o inferior a 135 cm de altura, ¿qué dispositivos de seguridad deben utilizar?</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -821,12 +821,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Es aconsejable evitar las comidas copiosas si se v</t>
+          <t>Entre los factores que favorecen la aparición de l</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Es aconsejable evitar las comidas copiosas si se va a conducir un vehículo ya que, en general, suelen producir...</t>
+          <t>Entre los factores que favorecen la aparición de la fatiga en el conductor se encuentra:</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -856,12 +856,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Si vamos a realizar un desplazamiento largo, para</t>
+          <t>Es aconsejable evitar las comidas copiosas si se v</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Si vamos a realizar un desplazamiento largo, para reducir la posibilidad de aparición de la somnolencia durante la conducción es aconsejable...</t>
+          <t>Es aconsejable evitar las comidas copiosas si se va a conducir un vehículo ya que, en general, suelen producir...</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -886,35 +886,105 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Si vamos a realizar un desplazamiento largo, para</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Si vamos a realizar un desplazamiento largo, para reducir la posibilidad de aparición de la somnolencia durante la conducción es aconsejable...</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>T10 TECNICAS COND</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Si se modifica la aerodinámica del vehículo añadie</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Si se modifica la aerodinámica del vehículo añadiendo elementos para hacerlo más atractivo...</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T10 TECNICAS COND</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A una motocicleta con motor de combustión interna,</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>A una motocicleta con motor de combustión interna, ¿se le permite circular sin tubo de escape?</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,65 +536,65 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T05</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Transporta en su turismo una carga que sobresale p</t>
+          <t>¿A qué vehículos de transporte de mercancías prohí</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Transporta en su turismo una carga que sobresale por la parte trasera, ¿debe señalizarla si circula de día?</t>
+          <t>¿A qué vehículos de transporte de mercancías prohíbe pasar esta señal?</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>El consumo de alcohol, ¿deteriora las capacidades</t>
+          <t>Transporta en su turismo una carga que sobresale p</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>El consumo de alcohol, ¿deteriora las capacidades para conducir con seguridad?</t>
+          <t>Transporta en su turismo una carga que sobresale por la parte trasera, ¿debe señalizarla si circula de día?</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -606,30 +606,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Circula por un carril y sobre él encuentra un semá</t>
+          <t>El consumo de alcohol, ¿deteriora las capacidades</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Circula por un carril y sobre él encuentra un semáforo con una luz roja en forma de aspa; ¿qué debe hacer?</t>
+          <t>El consumo de alcohol, ¿deteriora las capacidades para conducir con seguridad?</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -641,17 +641,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Si conduce una motocicleta con un pasajero, ¿qué d</t>
+          <t>Circula por un carril y sobre él encuentra un semá</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Si conduce una motocicleta con un pasajero, ¿qué debe tener en cuenta?</t>
+          <t>Circula por un carril y sobre él encuentra un semáforo con una luz roja en forma de aspa; ¿qué debe hacer?</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -681,12 +681,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Circular por debajo de la velocidad mínima permiti</t>
+          <t>Si conduce una motocicleta con un pasajero, ¿qué d</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Circular por debajo de la velocidad mínima permitida, ¿podría ser un factor de riesgo?</t>
+          <t>Si conduce una motocicleta con un pasajero, ¿qué debe tener en cuenta?</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -716,12 +716,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>El calor excesivo en el interior del vehículo, ¿pu</t>
+          <t>Circular por debajo de la velocidad mínima permiti</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>El calor excesivo en el interior del vehículo, ¿puede aumentar el riesgo en la conducción?</t>
+          <t>Circular por debajo de la velocidad mínima permitida, ¿podría ser un factor de riesgo?</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -751,12 +751,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>¿Cómo debe colocar el navegador GPS portátil en el</t>
+          <t>El calor excesivo en el interior del vehículo, ¿pu</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>¿Cómo debe colocar el navegador GPS portátil en el vehículo?</t>
+          <t>El calor excesivo en el interior del vehículo, ¿puede aumentar el riesgo en la conducción?</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -781,17 +781,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T01 Uso vias públicas</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Si los ocupantes de los asientos traseros de un ve</t>
+          <t>¿Cómo debe colocar el navegador GPS portátil en el</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Si los ocupantes de los asientos traseros de un vehículo son menores de edad y de estatura igual o inferior a 135 cm de altura, ¿qué dispositivos de seguridad deben utilizar?</t>
+          <t>¿Cómo debe colocar el navegador GPS portátil en el vehículo?</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -816,17 +816,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T01 Uso vias públicas</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Entre los factores que favorecen la aparición de l</t>
+          <t>Si los ocupantes de los asientos traseros de un ve</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Entre los factores que favorecen la aparición de la fatiga en el conductor se encuentra:</t>
+          <t>Si los ocupantes de los asientos traseros de un vehículo son menores de edad y de estatura igual o inferior a 135 cm de altura, ¿qué dispositivos de seguridad deben utilizar?</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -856,12 +856,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Es aconsejable evitar las comidas copiosas si se v</t>
+          <t>Entre los factores que favorecen la aparición de l</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Es aconsejable evitar las comidas copiosas si se va a conducir un vehículo ya que, en general, suelen producir...</t>
+          <t>Entre los factores que favorecen la aparición de la fatiga en el conductor se encuentra:</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -891,12 +891,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Si vamos a realizar un desplazamiento largo, para</t>
+          <t>Es aconsejable evitar las comidas copiosas si se v</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Si vamos a realizar un desplazamiento largo, para reducir la posibilidad de aparición de la somnolencia durante la conducción es aconsejable...</t>
+          <t>Es aconsejable evitar las comidas copiosas si se va a conducir un vehículo ya que, en general, suelen producir...</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -921,17 +921,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T10 TECNICAS COND</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Si se modifica la aerodinámica del vehículo añadie</t>
+          <t>Si vamos a realizar un desplazamiento largo, para</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Si se modifica la aerodinámica del vehículo añadiendo elementos para hacerlo más atractivo...</t>
+          <t>Si vamos a realizar un desplazamiento largo, para reducir la posibilidad de aparición de la somnolencia durante la conducción es aconsejable...</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -961,30 +961,65 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>Si se modifica la aerodinámica del vehículo añadie</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Si se modifica la aerodinámica del vehículo añadiendo elementos para hacerlo más atractivo...</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>T10 TECNICAS COND</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>A una motocicleta con motor de combustión interna,</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>A una motocicleta con motor de combustión interna, ¿se le permite circular sin tubo de escape?</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1023,6 +1023,41 @@
         <v>100</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>El conductor del vehículo de la fotografía está in</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>El conductor del vehículo de la fotografía está indicando que va a...</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1058,6 +1058,41 @@
         <v>100</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>¿Qué es un microsueño?</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>¿Qué es un microsueño?</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1093,6 +1093,41 @@
         <v>100</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Esta señal prohíbe:</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Esta señal prohíbe:</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1128,6 +1128,76 @@
         <v>100</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>El permiso de conducción de la clase A1, ¿autoriza</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>El permiso de conducción de la clase A1, ¿autoriza a conducir motocicletas con sidecar?</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Una ambulancia circula en servicio urgente por una</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Una ambulancia circula en servicio urgente por una vía urbana, ¿están obligados a utilizar el cinturón de seguridad el conductor y los pasajeros?</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,65 +571,65 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T05</t>
+          <t>T02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Transporta en su turismo una carga que sobresale p</t>
+          <t>Circula con su turismo por el arcén de una autovía</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Transporta en su turismo una carga que sobresale por la parte trasera, ¿debe señalizarla si circula de día?</t>
+          <t>Circula con su turismo por el arcén de una autovía para facilitar el adelantamiento al camión. ¿Es correcto su comportamiento?</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>El consumo de alcohol, ¿deteriora las capacidades</t>
+          <t>Transporta en su turismo una carga que sobresale p</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>El consumo de alcohol, ¿deteriora las capacidades para conducir con seguridad?</t>
+          <t>Transporta en su turismo una carga que sobresale por la parte trasera, ¿debe señalizarla si circula de día?</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -641,30 +641,30 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Circula por un carril y sobre él encuentra un semá</t>
+          <t>El consumo de alcohol, ¿deteriora las capacidades</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Circula por un carril y sobre él encuentra un semáforo con una luz roja en forma de aspa; ¿qué debe hacer?</t>
+          <t>El consumo de alcohol, ¿deteriora las capacidades para conducir con seguridad?</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -676,17 +676,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Si conduce una motocicleta con un pasajero, ¿qué d</t>
+          <t>Circula por un carril y sobre él encuentra un semá</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Si conduce una motocicleta con un pasajero, ¿qué debe tener en cuenta?</t>
+          <t>Circula por un carril y sobre él encuentra un semáforo con una luz roja en forma de aspa; ¿qué debe hacer?</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -716,12 +716,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Circular por debajo de la velocidad mínima permiti</t>
+          <t>Si conduce una motocicleta con un pasajero, ¿qué d</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Circular por debajo de la velocidad mínima permitida, ¿podría ser un factor de riesgo?</t>
+          <t>Si conduce una motocicleta con un pasajero, ¿qué debe tener en cuenta?</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -751,12 +751,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>El calor excesivo en el interior del vehículo, ¿pu</t>
+          <t>Circular por debajo de la velocidad mínima permiti</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>El calor excesivo en el interior del vehículo, ¿puede aumentar el riesgo en la conducción?</t>
+          <t>Circular por debajo de la velocidad mínima permitida, ¿podría ser un factor de riesgo?</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -786,12 +786,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>¿Cómo debe colocar el navegador GPS portátil en el</t>
+          <t>El calor excesivo en el interior del vehículo, ¿pu</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>¿Cómo debe colocar el navegador GPS portátil en el vehículo?</t>
+          <t>El calor excesivo en el interior del vehículo, ¿puede aumentar el riesgo en la conducción?</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -816,17 +816,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T01 Uso vias públicas</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Si los ocupantes de los asientos traseros de un ve</t>
+          <t>¿Cómo debe colocar el navegador GPS portátil en el</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Si los ocupantes de los asientos traseros de un vehículo son menores de edad y de estatura igual o inferior a 135 cm de altura, ¿qué dispositivos de seguridad deben utilizar?</t>
+          <t>¿Cómo debe colocar el navegador GPS portátil en el vehículo?</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -851,17 +851,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T01 Uso vias públicas</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Entre los factores que favorecen la aparición de l</t>
+          <t>Si los ocupantes de los asientos traseros de un ve</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Entre los factores que favorecen la aparición de la fatiga en el conductor se encuentra:</t>
+          <t>Si los ocupantes de los asientos traseros de un vehículo son menores de edad y de estatura igual o inferior a 135 cm de altura, ¿qué dispositivos de seguridad deben utilizar?</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -891,12 +891,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Es aconsejable evitar las comidas copiosas si se v</t>
+          <t>Entre los factores que favorecen la aparición de l</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Es aconsejable evitar las comidas copiosas si se va a conducir un vehículo ya que, en general, suelen producir...</t>
+          <t>Entre los factores que favorecen la aparición de la fatiga en el conductor se encuentra:</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -926,12 +926,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Si vamos a realizar un desplazamiento largo, para</t>
+          <t>Es aconsejable evitar las comidas copiosas si se v</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Si vamos a realizar un desplazamiento largo, para reducir la posibilidad de aparición de la somnolencia durante la conducción es aconsejable...</t>
+          <t>Es aconsejable evitar las comidas copiosas si se va a conducir un vehículo ya que, en general, suelen producir...</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -956,17 +956,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T10 TECNICAS COND</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Si se modifica la aerodinámica del vehículo añadie</t>
+          <t>Si vamos a realizar un desplazamiento largo, para</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Si se modifica la aerodinámica del vehículo añadiendo elementos para hacerlo más atractivo...</t>
+          <t>Si vamos a realizar un desplazamiento largo, para reducir la posibilidad de aparición de la somnolencia durante la conducción es aconsejable...</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -996,12 +996,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A una motocicleta con motor de combustión interna,</t>
+          <t>Si se modifica la aerodinámica del vehículo añadie</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A una motocicleta con motor de combustión interna, ¿se le permite circular sin tubo de escape?</t>
+          <t>Si se modifica la aerodinámica del vehículo añadiendo elementos para hacerlo más atractivo...</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1026,17 +1026,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T02</t>
+          <t>T10 TECNICAS COND</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>El conductor del vehículo de la fotografía está in</t>
+          <t>A una motocicleta con motor de combustión interna,</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>El conductor del vehículo de la fotografía está indicando que va a...</t>
+          <t>A una motocicleta con motor de combustión interna, ¿se le permite circular sin tubo de escape?</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1061,17 +1061,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>¿Qué es un microsueño?</t>
+          <t>El conductor del vehículo de la fotografía está in</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>¿Qué es un microsueño?</t>
+          <t>El conductor del vehículo de la fotografía está indicando que va a...</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1096,17 +1096,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Esta señal prohíbe:</t>
+          <t>¿Qué es un microsueño?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Esta señal prohíbe:</t>
+          <t>¿Qué es un microsueño?</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1131,17 +1131,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T06</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>El permiso de conducción de la clase A1, ¿autoriza</t>
+          <t>Esta señal prohíbe:</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>El permiso de conducción de la clase A1, ¿autoriza a conducir motocicletas con sidecar?</t>
+          <t>Esta señal prohíbe:</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1166,35 +1166,70 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>T06</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>El permiso de conducción de la clase A1, ¿autoriza</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>El permiso de conducción de la clase A1, ¿autoriza a conducir motocicletas con sidecar?</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>T05</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Una ambulancia circula en servicio urgente por una</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Una ambulancia circula en servicio urgente por una vía urbana, ¿están obligados a utilizar el cinturón de seguridad el conductor y los pasajeros?</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>100</v>
       </c>
     </row>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1233,6 +1233,41 @@
         <v>100</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>¿Qué indica lamarca de color blanco de la derecha?</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>¿Qué indica lamarca de color blanco de la derecha?</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/estadisticas.xlsx
+++ b/estadisticas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1268,6 +1268,41 @@
         <v>100</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>T10 TECNICAS COND</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>La distribución de la carga en un vehículo, ¿afect</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>La distribución de la carga en un vehículo, ¿afecta al consumo de combustible?</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
